--- a/data/trans_orig/P21D_2_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,82 +730,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3764</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1145</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3420</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1145</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212873</t>
+          <t>212529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>437382</t>
+          <t>437399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177247</t>
+          <t>177803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>174327</t>
+          <t>173945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354202</t>
+          <t>354523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414324</t>
+          <t>414323</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410743</t>
+          <t>410728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74914</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>78788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>487283</t>
+          <t>487153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>437937</t>
+          <t>438673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>450898</t>
+          <t>451163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320821</t>
+          <t>322066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>332955</t>
+          <t>333168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>765323</t>
+          <t>765559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>782227</t>
+          <t>781341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>49616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200146</t>
+          <t>201272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214518</t>
+          <t>214425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381178</t>
+          <t>380671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>408040</t>
+          <t>408281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>590297</t>
+          <t>588923</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>619437</t>
+          <t>619247</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118553</t>
+          <t>119502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309663</t>
+          <t>309438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316725</t>
+          <t>316734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>431831</t>
+          <t>431696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>439386</t>
+          <t>439658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>44969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86369</t>
+          <t>85725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1586436</t>
+          <t>1584509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1608742</t>
+          <t>1607819</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1490200</t>
+          <t>1491921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1521641</t>
+          <t>1521298</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3084663</t>
+          <t>3085307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3123833</t>
+          <t>3126063</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_2_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_2_R-Clase-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>215148</t>
+          <t>232008</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212529</t>
+          <t>229220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>440087</t>
+          <t>476418</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>437399</t>
+          <t>473052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>180787</t>
+          <t>196001</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177803</t>
+          <t>192356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,17 +1216,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>177298</t>
+          <t>195812</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173945</t>
+          <t>192518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>358084</t>
+          <t>391813</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354523</t>
+          <t>387519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414323</t>
+          <t>187912</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410728</t>
+          <t>184328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77682</t>
+          <t>84706</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75053</t>
+          <t>81219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>86147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>492005</t>
+          <t>272618</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>487153</t>
+          <t>268083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>274620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,22 +1824,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>446104</t>
+          <t>502232</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>438673</t>
+          <t>494953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451163</t>
+          <t>507332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>328440</t>
+          <t>373658</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322066</t>
+          <t>366716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333168</t>
+          <t>379363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>774544</t>
+          <t>875889</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>765559</t>
+          <t>865034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>781341</t>
+          <t>883277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49616</t>
+          <t>50044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>208984</t>
+          <t>244640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201272</t>
+          <t>234475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214425</t>
+          <t>252979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>398688</t>
+          <t>373080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>380671</t>
+          <t>364313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>408281</t>
+          <t>378772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>607672</t>
+          <t>617720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>588923</t>
+          <t>604435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>619247</t>
+          <t>626980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>416438</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>416438</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>416438</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>638539</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>638539</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>638539</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>122610</t>
+          <t>116717</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119502</t>
+          <t>112582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>314108</t>
+          <t>347532</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309438</t>
+          <t>338023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316734</t>
+          <t>351791</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>436719</t>
+          <t>464250</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>431696</t>
+          <t>455148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>439658</t>
+          <t>468699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>58347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85725</t>
+          <t>91686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1597747</t>
+          <t>1491913</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1584509</t>
+          <t>1479201</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1607819</t>
+          <t>1501912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1511364</t>
+          <t>1606796</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1491921</t>
+          <t>1593848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1521298</t>
+          <t>1616622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3109111</t>
+          <t>3098709</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3085307</t>
+          <t>3081119</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3126063</t>
+          <t>3114458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1547797</t>
+          <t>1647351</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1547797</t>
+          <t>1647351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1547797</t>
+          <t>1647351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3171032</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3171032</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3171032</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
